--- a/public/files/planilla_datos_oma.xlsx
+++ b/public/files/planilla_datos_oma.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
-    <t>42° OMA - ALUMNOS QUE PARTICIPAN EN EL CERTAMEN INTERESCOLAR 2025</t>
+    <t>43° OMA - ALUMNOS QUE PARTICIPAN EN EL CERTAMEN INTERESCOLAR 2026</t>
   </si>
   <si>
     <t>Datos de la escuela:</t>
